--- a/y12901/长上下文截断审计/demo_output/版本对比.xlsx
+++ b/y12901/长上下文截断审计/demo_output/版本对比.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:20:11</t>
+          <t>2026-06-17 16:30:51</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:20:11</t>
+          <t>2026-06-17 16:30:51</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:20:11</t>
+          <t>2026-06-17 16:30:51</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:20:11</t>
+          <t>2026-06-17 16:30:51</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:20:11</t>
+          <t>2026-06-17 16:30:51</t>
         </is>
       </c>
     </row>
